--- a/data/trans_dic/P25C$smedicoempresa_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,66</t>
+          <t>0,06; 0,62</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1390</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1629</t>
+          <t>0; 2090</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1769</t>
+          <t>0; 1708</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8694</t>
+          <t>0; 9008</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1220</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7120</t>
+          <t>0; 6189</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1624</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1329</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1515</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2880</t>
+          <t>0; 2784</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1211</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2818</t>
+          <t>0; 2851</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6642</t>
+          <t>0; 7332</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2565</t>
+          <t>0; 1917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>500; 7838</t>
+          <t>701; 7321</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$smedicoempresa_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Habitat-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,09; 1,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,62</t>
+          <t>0,06; 0,66</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2090</t>
+          <t>0; 1654</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1708</t>
+          <t>0; 2404</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9008</t>
+          <t>0; 6900</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6189</t>
+          <t>0; 6203</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2784</t>
+          <t>0; 3335</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2851</t>
+          <t>0; 2871</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7332</t>
+          <t>573; 7275</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1917</t>
+          <t>0; 1844</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>701; 7321</t>
+          <t>627; 6792</t>
         </is>
       </c>
     </row>
